--- a/test_files/file2.xlsx
+++ b/test_files/file2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Datetime</t>
   </si>
@@ -25,43 +25,31 @@
     <t>Qty</t>
   </si>
   <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>INR</t>
-  </si>
-  <si>
-    <t>Extra</t>
-  </si>
-  <si>
-    <t>2024-04-22 12:00:00</t>
-  </si>
-  <si>
-    <t>invalid_date</t>
+    <t>Lead</t>
+  </si>
+  <si>
+    <t>Extra Info</t>
   </si>
   <si>
     <t>20-04-2024 10:00:00</t>
   </si>
   <si>
+    <t>22-04-2024 12:00:00</t>
+  </si>
+  <si>
+    <t>BTC</t>
+  </si>
+  <si>
     <t>SOL</t>
   </si>
   <si>
-    <t>DOT</t>
-  </si>
-  <si>
-    <t>BTC</t>
+    <t>Ravi</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
+    <t>Confirmed</t>
   </si>
 </sst>
 </file>
@@ -419,10 +407,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,85 +426,36 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>1.5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>500</v>
-      </c>
-      <c r="E2">
-        <v>40000</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
-      <c r="D3">
-        <v>500</v>
-      </c>
-      <c r="E3">
-        <v>40000</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="B4" t="s">
+      <c r="D3" t="s">
         <v>10</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4">
-        <v>8000</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>1.5</v>
-      </c>
-      <c r="D5">
-        <v>1000</v>
-      </c>
-      <c r="E5">
-        <v>80000</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
